--- a/Meteo_ValledelEria_datos.xlsx
+++ b/Meteo_ValledelEria_datos.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Horario" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Horario'!$A$1:$E$2128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Horario'!$A$1:$E$2144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -512,21 +512,21 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Excel generado: 18/10/2026 15:49 (hora de España)</t>
+          <t>Excel generado: 19/10/2026 07:50 (hora de España)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Última captura de datos (UTC): 2026-10-18 13:49</t>
+          <t>Última captura de datos (UTC): 2026-10-19 05:50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Horas con algún dato en la hoja Horario: 2127 · Días en la hoja Diario: 91</t>
+          <t>Horas con algún dato en la hoja Horario: 2143 · Días en la hoja Diario: 92</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q96"/>
+  <dimension ref="A1:Q97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -882,11 +882,11 @@
       <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>24</v>
+      <c r="F7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="H7" s="11" t="n"/>
       <c r="I7" s="11" t="n"/>
@@ -896,11 +896,11 @@
       <c r="M7" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="12" t="n">
-        <v>24</v>
+      <c r="N7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="n">
+        <v>23</v>
       </c>
       <c r="P7" s="11" t="n"/>
       <c r="Q7" s="11" t="n"/>
@@ -1090,7 +1090,7 @@
       <c r="G13" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="9" t="n">
         <v>0</v>
       </c>
       <c r="I13" s="11" t="n"/>
@@ -1106,7 +1106,7 @@
       <c r="O13" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="P13" s="11" t="n">
+      <c r="P13" s="9" t="n">
         <v>0.2</v>
       </c>
       <c r="Q13" s="11" t="n"/>
@@ -1948,7 +1948,7 @@
       <c r="H36" s="11" t="n">
         <v>2.5</v>
       </c>
-      <c r="I36" s="11" t="n">
+      <c r="I36" s="9" t="n">
         <v>2.9</v>
       </c>
       <c r="J36" s="9" t="n"/>
@@ -4963,23 +4963,23 @@
       <c r="A96" s="8" t="n">
         <v>46313</v>
       </c>
-      <c r="B96" s="9" t="n">
+      <c r="B96" s="11" t="n">
         <v>4.2</v>
       </c>
-      <c r="C96" s="9" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="D96" s="9" t="n">
-        <v>8.50625</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="F96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="G96" s="10" t="n">
-        <v>16</v>
+      <c r="C96" s="11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>9.408333333333333</v>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>24</v>
       </c>
       <c r="H96" s="9" t="n">
         <v>5.7</v>
@@ -4987,28 +4987,81 @@
       <c r="I96" s="9" t="n">
         <v>27.7</v>
       </c>
-      <c r="J96" s="9" t="n">
+      <c r="J96" s="11" t="n">
         <v>5.7</v>
       </c>
-      <c r="K96" s="9" t="n">
+      <c r="K96" s="11" t="n">
         <v>14.3</v>
       </c>
-      <c r="L96" s="9" t="n">
-        <v>9.543750000000001</v>
-      </c>
-      <c r="M96" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="N96" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O96" s="10" t="n">
-        <v>16</v>
+      <c r="L96" s="11" t="n">
+        <v>10.05416666666667</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="N96" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="12" t="n">
+        <v>24</v>
       </c>
       <c r="P96" s="9" t="n">
         <v>0.4</v>
       </c>
       <c r="Q96" s="9" t="n">
+        <v>19.1</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="8" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" s="9" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>2.9625</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="F97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G97" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="H97" s="9" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="I97" s="9" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L97" s="9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M97" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="N97" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O97" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="P97" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q97" s="9" t="n">
         <v>19.1</v>
       </c>
     </row>
@@ -5028,7 +5081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2128"/>
+  <dimension ref="A1:E2144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5386,12 +5439,12 @@
         <v>46224</v>
       </c>
       <c r="B26" s="14" t="n"/>
-      <c r="C26" s="11" t="n">
-        <v>0</v>
+      <c r="C26" s="15" t="n">
+        <v>120</v>
       </c>
       <c r="D26" s="14" t="n"/>
-      <c r="E26" s="11" t="n">
-        <v>0</v>
+      <c r="E26" s="15" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="27">
@@ -36954,8 +37007,280 @@
         <v>0</v>
       </c>
     </row>
+    <row r="2129">
+      <c r="A2129" s="13" t="n">
+        <v>46313.66666666666</v>
+      </c>
+      <c r="B2129" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="C2129" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2129" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2129" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2130">
+      <c r="A2130" s="13" t="n">
+        <v>46313.70833333334</v>
+      </c>
+      <c r="B2130" s="11" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="C2130" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2130" s="11" t="n">
+        <v>14.3</v>
+      </c>
+      <c r="E2130" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="13" t="n">
+        <v>46313.75</v>
+      </c>
+      <c r="B2131" s="11" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="C2131" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2131" s="11" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="E2131" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="13" t="n">
+        <v>46313.79166666666</v>
+      </c>
+      <c r="B2132" s="11" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C2132" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2132" s="11" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="E2132" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="13" t="n">
+        <v>46313.83333333334</v>
+      </c>
+      <c r="B2133" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="C2133" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2133" s="11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E2133" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2134">
+      <c r="A2134" s="13" t="n">
+        <v>46313.875</v>
+      </c>
+      <c r="B2134" s="11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="C2134" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2134" s="11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E2134" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2135">
+      <c r="A2135" s="13" t="n">
+        <v>46313.91666666666</v>
+      </c>
+      <c r="B2135" s="11" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="C2135" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2135" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2135" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="13" t="n">
+        <v>46313.95833333334</v>
+      </c>
+      <c r="B2136" s="11" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="C2136" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2136" s="11" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="E2136" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="13" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2137" s="11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="C2137" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2137" s="11" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="E2137" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="13" t="n">
+        <v>46314.04166666666</v>
+      </c>
+      <c r="B2138" s="11" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="C2138" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2138" s="11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="E2138" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="13" t="n">
+        <v>46314.08333333334</v>
+      </c>
+      <c r="B2139" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C2139" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2139" s="11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E2139" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="13" t="n">
+        <v>46314.125</v>
+      </c>
+      <c r="B2140" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2140" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2140" s="11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E2140" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="13" t="n">
+        <v>46314.16666666666</v>
+      </c>
+      <c r="B2141" s="11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C2141" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2141" s="11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E2141" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2142">
+      <c r="A2142" s="13" t="n">
+        <v>46314.20833333334</v>
+      </c>
+      <c r="B2142" s="11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C2142" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2142" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E2142" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2143">
+      <c r="A2143" s="13" t="n">
+        <v>46314.25</v>
+      </c>
+      <c r="B2143" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2143" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2143" s="11" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E2143" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2144">
+      <c r="A2144" s="13" t="n">
+        <v>46314.29166666666</v>
+      </c>
+      <c r="B2144" s="11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C2144" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2144" s="11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E2144" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E2128"/>
+  <autoFilter ref="A1:E2144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>